--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -20513,16 +20513,16 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -27163,6 +27163,154 @@
       <c r="BC157" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27199,7 +27347,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -27282,7 +27430,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -27292,7 +27440,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
@@ -27344,7 +27492,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>13</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -1702,9 +1696,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -1998,9 +1986,6 @@
       <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -2643,7 +2628,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -2790,9 +2775,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -4666,9 +4648,6 @@
       <c r="O25" t="n">
         <v>17</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5059,9 +5038,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5455,9 +5431,6 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -5603,9 +5576,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -5751,9 +5721,6 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -6396,7 +6363,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -6543,9 +6510,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -8419,9 +8383,6 @@
       <c r="O47" t="n">
         <v>14</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8812,9 +8773,6 @@
       <c r="O49" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -9208,9 +9166,6 @@
       <c r="O51" t="n">
         <v>3</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.04065810840590128</v>
       </c>
@@ -9356,9 +9311,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -9504,9 +9456,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -10149,7 +10098,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -10296,9 +10245,6 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -11876,9 +11822,6 @@
       <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.02938249455615832</v>
       </c>
@@ -12024,9 +11967,6 @@
       <c r="O68" t="n">
         <v>15</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.007023699528494134</v>
       </c>
@@ -12172,9 +12112,6 @@
       <c r="O69" t="n">
         <v>10</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="S69" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12565,9 +12502,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -12961,9 +12895,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -13109,9 +13040,6 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -13257,9 +13185,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -13653,9 +13578,6 @@
       <c r="O77" t="n">
         <v>6</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1134756279883097</v>
       </c>
@@ -13902,7 +13824,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14049,9 +13971,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -15629,9 +15548,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15777,9 +15693,6 @@
       <c r="O90" t="n">
         <v>9</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.004214219717096481</v>
       </c>
@@ -15925,9 +15838,6 @@
       <c r="O91" t="n">
         <v>11</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16318,9 +16228,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -16714,9 +16621,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -16862,9 +16766,6 @@
       <c r="O96" t="n">
         <v>3</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -17010,9 +16911,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17406,9 +17304,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.03782520932943658</v>
       </c>
@@ -17655,7 +17550,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -17802,9 +17697,6 @@
       <c r="O101" t="n">
         <v>4</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -18198,9 +18090,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -19826,9 +19715,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -19974,9 +19860,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -20370,9 +20253,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -20518,9 +20398,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -20666,9 +20543,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21062,9 +20936,6 @@
       <c r="O121" t="n">
         <v>4</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -21311,7 +21182,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -21458,9 +21329,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -21854,9 +21722,6 @@
       <c r="O125" t="n">
         <v>2</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -22002,9 +21867,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -22150,9 +22012,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -22298,9 +22157,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22446,9 +22302,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -22594,9 +22447,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22742,9 +22592,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22890,9 +22737,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -23038,9 +22882,6 @@
       <c r="O133" t="n">
         <v>6</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.02203687091711874</v>
       </c>
@@ -23186,9 +23027,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -23582,9 +23420,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.003875939847584092</v>
       </c>
@@ -23730,9 +23565,6 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -24126,9 +23958,6 @@
       <c r="O139" t="n">
         <v>2</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -24522,9 +24351,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -24670,9 +24496,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -24818,9 +24641,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -24966,9 +24786,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -25114,9 +24931,6 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -25262,9 +25076,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -25410,9 +25221,6 @@
       <c r="O147" t="n">
         <v>2</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -25558,9 +25366,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -25706,9 +25511,6 @@
       <c r="O149" t="n">
         <v>2</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -25854,9 +25656,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.001633616815131532</v>
       </c>
@@ -26002,9 +25801,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -26150,9 +25946,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -26546,9 +26339,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -26694,9 +26484,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -27090,9 +26877,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -27236,9 +27020,6 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q158" t="n">
         <v>0</v>
       </c>
       <c r="R158" t="n">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -22877,13 +22877,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.02570968273663853</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -19816,12 +19816,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19855,22 +19855,19 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_CA_ON_PHO_IDTO_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -19890,12 +19887,12 @@
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_CA_ON_PHO_IDTO_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -19903,47 +19900,47 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19975,12 +19972,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20014,29 +20011,29 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_CA_ON_PHO_IDTO_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_CA_ON_PHO_IDTO_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>Salmonella Typhi</t>
+          <t>Typhoid Fever</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -20046,7 +20043,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -20061,7 +20058,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -20096,17 +20093,17 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+          <t>PHO IDTO current-year monthly preliminary typhoid fever notifications, separate from paratyphoid fever; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -20124,12 +20121,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1180</t>
+          <t>SER_CA_ON_PHO_IDTO_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -20137,47 +20134,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20209,12 +20206,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20261,68 +20258,82 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ117" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20349,17 +20360,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20393,81 +20404,170 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>3</v>
-      </c>
-      <c r="R118" t="n">
-        <v>0.005813909771376137</v>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN118" t="b">
+        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ118" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20499,12 +20599,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20551,82 +20651,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20653,17 +20739,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20697,170 +20783,81 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20892,12 +20889,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20931,13 +20928,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0.07565041865887316</v>
+        <v>0</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -20946,7 +20943,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -20971,7 +20968,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -20984,42 +20981,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21051,12 +21048,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21090,29 +21087,29 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>Typhoid fever</t>
+          <t>Tyfoidfeber</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -21122,7 +21119,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -21137,7 +21134,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -21172,17 +21169,17 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -21205,7 +21202,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -21218,42 +21215,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21285,12 +21282,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21324,13 +21321,13 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R123" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.07565041865887316</v>
       </c>
       <c r="S123" t="inlineStr">
         <is>
@@ -21339,7 +21336,7 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21364,7 +21361,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21377,42 +21374,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21444,12 +21441,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21483,29 +21480,29 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>Tyfoidfeber</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -21515,7 +21512,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -21530,7 +21527,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -21565,17 +21562,17 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN124" t="b">
@@ -21598,7 +21595,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21611,42 +21608,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21678,12 +21675,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21708,7 +21705,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -21723,75 +21720,89 @@
         <v>2</v>
       </c>
       <c r="R125" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21818,17 +21829,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21853,7 +21864,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21862,81 +21873,170 @@
         </is>
       </c>
       <c r="N126" t="n">
+        <v>2</v>
+      </c>
+      <c r="O126" t="n">
+        <v>2</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
         <v>1</v>
       </c>
-      <c r="O126" t="n">
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
         <v>1</v>
       </c>
-      <c r="R126" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP126" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
-      <c r="AT126" t="n">
-        <v>0</v>
-      </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21998,7 +22098,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22007,13 +22107,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R127" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22143,7 +22243,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22152,13 +22252,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22288,7 +22388,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22297,13 +22397,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22433,7 +22533,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22442,13 +22542,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22578,7 +22678,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22723,7 +22823,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22732,13 +22832,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R132" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22838,12 +22938,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22868,22 +22968,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02570968273663853</v>
+        <v>0</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22916,42 +23016,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22983,12 +23083,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23013,104 +23113,90 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R134" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23137,17 +23223,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23181,170 +23267,81 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.02570968273663853</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV135" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23376,12 +23373,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23421,75 +23418,89 @@
         <v>2</v>
       </c>
       <c r="R136" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23516,17 +23527,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23560,22 +23571,39 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O137" t="n">
-        <v>3</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.05306927477386519</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -23583,6 +23611,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23595,12 +23681,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -23608,47 +23694,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23675,17 +23761,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23719,170 +23805,81 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O138" t="n">
-        <v>3</v>
-      </c>
-      <c r="U138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA138" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ138" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -23914,12 +23911,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23953,13 +23950,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O139" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R139" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23968,7 +23965,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -23993,7 +23990,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -24006,42 +24003,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24073,12 +24070,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24112,24 +24109,24 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
@@ -24159,7 +24156,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -24194,17 +24191,17 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -24227,7 +24224,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -24240,42 +24237,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24307,12 +24304,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24346,81 +24343,95 @@
         </is>
       </c>
       <c r="N141" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" t="n">
+        <v>2</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
         <v>1</v>
       </c>
-      <c r="O141" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP141" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
-      <c r="AT141" t="n">
-        <v>0</v>
-      </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24447,17 +24458,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24482,7 +24493,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24491,81 +24502,170 @@
         </is>
       </c>
       <c r="N142" t="n">
+        <v>2</v>
+      </c>
+      <c r="O142" t="n">
+        <v>2</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
         <v>1</v>
       </c>
-      <c r="O142" t="n">
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
         <v>1</v>
       </c>
-      <c r="R142" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP142" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
-      <c r="AT142" t="n">
-        <v>0</v>
-      </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24597,12 +24697,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24627,7 +24727,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24636,13 +24736,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24675,42 +24775,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24772,7 +24872,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24917,7 +25017,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24926,13 +25026,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25062,7 +25162,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25071,13 +25171,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25207,7 +25307,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25216,13 +25316,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25352,7 +25452,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25497,7 +25597,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25642,7 +25742,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25651,13 +25751,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25757,12 +25857,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25787,22 +25887,22 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25835,42 +25935,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25902,12 +26002,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25932,104 +26032,90 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R152" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26056,17 +26142,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26100,170 +26186,81 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
-      </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP153" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT153" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV153" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26295,12 +26292,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26334,81 +26331,95 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26435,17 +26446,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26479,22 +26490,39 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -26502,6 +26530,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26514,12 +26600,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -26527,47 +26613,47 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26594,17 +26680,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26643,165 +26729,76 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
+      <c r="R156" t="n">
+        <v>0</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -26833,12 +26830,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26872,81 +26869,95 @@
         </is>
       </c>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT157" t="n">
         <v>1</v>
       </c>
-      <c r="O157" t="n">
-        <v>1</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP157" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
-      <c r="AT157" t="n">
-        <v>0</v>
-      </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26973,123 +26984,502 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>1</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>D124</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Typhoid fever</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>伤寒</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="K160" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N158" t="n">
-        <v>0</v>
-      </c>
-      <c r="O158" t="n">
-        <v>0</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0</v>
-      </c>
-      <c r="S158" t="inlineStr">
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO158" t="inlineStr">
+      <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP158" t="inlineStr">
+      <c r="AP160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR158" t="inlineStr">
+      <c r="AR160" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS158" t="inlineStr"/>
-      <c r="AT158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU158" t="inlineStr">
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV158" t="inlineStr">
+      <c r="AV160" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW158" t="inlineStr">
+      <c r="AW160" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX158" t="inlineStr">
+      <c r="AX160" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY158" t="inlineStr">
+      <c r="AY160" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ158" t="inlineStr">
+      <c r="AZ160" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA158" t="inlineStr">
+      <c r="BA160" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB158" t="inlineStr">
+      <c r="BB160" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC158" t="inlineStr">
+      <c r="BC160" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27211,7 +27601,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -27221,7 +27611,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -27241,7 +27631,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -27273,7 +27663,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -27485,6 +27485,151 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="n">
+        <v>2</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27518,7 +27663,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -27601,7 +27746,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -27611,7 +27756,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -27663,7 +27808,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -24304,12 +24304,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24343,13 +24343,13 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O141" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R141" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.07565041865887316</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -24383,7 +24383,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -24396,42 +24396,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24463,12 +24463,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24502,29 +24502,29 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>Tyfoidfeber</t>
+          <t>Typhoid fever</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -24534,7 +24534,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -24549,7 +24549,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -24584,17 +24584,17 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24630,42 +24630,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24697,12 +24697,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24736,81 +24736,95 @@
         </is>
       </c>
       <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>2</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
         <v>1</v>
       </c>
-      <c r="O143" t="n">
-        <v>1</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP143" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
-      <c r="AT143" t="n">
-        <v>0</v>
-      </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24837,17 +24851,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24872,7 +24886,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24881,81 +24895,170 @@
         </is>
       </c>
       <c r="N144" t="n">
+        <v>2</v>
+      </c>
+      <c r="O144" t="n">
+        <v>2</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
         <v>1</v>
       </c>
-      <c r="O144" t="n">
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
         <v>1</v>
       </c>
-      <c r="R144" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
-      <c r="AT144" t="n">
-        <v>0</v>
-      </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24987,12 +25090,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25017,7 +25120,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25026,13 +25129,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25065,42 +25168,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25162,7 +25265,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25307,7 +25410,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25316,13 +25419,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25452,7 +25555,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25461,13 +25564,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25597,7 +25700,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25606,13 +25709,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R149" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25742,7 +25845,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25887,7 +25990,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -26032,7 +26135,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26041,13 +26144,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.001633616815131532</v>
+        <v>0</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26147,12 +26250,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26177,22 +26280,22 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26225,42 +26328,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26292,12 +26395,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26322,104 +26425,90 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26446,17 +26535,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26490,170 +26579,81 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP155" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AT155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV155" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26685,12 +26685,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26724,81 +26724,95 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26825,17 +26839,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26869,22 +26883,39 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -26892,6 +26923,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26904,12 +26993,12 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -26917,47 +27006,47 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26984,17 +27073,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27033,165 +27122,76 @@
       <c r="O158" t="n">
         <v>0</v>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ158" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -27223,12 +27223,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27262,81 +27262,95 @@
         </is>
       </c>
       <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT159" t="n">
         <v>1</v>
       </c>
-      <c r="O159" t="n">
-        <v>1</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
-      <c r="AT159" t="n">
-        <v>0</v>
-      </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27363,17 +27377,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27398,7 +27412,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27412,76 +27426,165 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27513,12 +27616,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27543,7 +27646,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27552,13 +27655,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R161" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27591,40 +27694,475 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW161" t="inlineStr">
+      <c r="AW162" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX161" t="inlineStr">
+      <c r="AX162" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY161" t="inlineStr">
+      <c r="AY162" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ161" t="inlineStr">
+      <c r="AZ162" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA161" t="inlineStr">
+      <c r="BA162" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB161" t="inlineStr">
+      <c r="BB162" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC161" t="inlineStr">
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>2</v>
+      </c>
+      <c r="O163" t="n">
+        <v>2</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27663,7 +28201,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -27746,7 +28284,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -27756,7 +28294,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -27776,7 +28314,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -27808,7 +28346,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -34010,12 +34010,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -34055,7 +34055,7 @@
         <v>2</v>
       </c>
       <c r="R190" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -34088,42 +34088,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34155,12 +34155,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -34194,95 +34194,81 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R191" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA191" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ191" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS191" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -34309,7 +34295,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -34358,98 +34344,23 @@
       <c r="O192" t="n">
         <v>3</v>
       </c>
+      <c r="R192" t="n">
+        <v>0.05306927477386519</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U192" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V192" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X192" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y192" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD192" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE192" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF192" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG192" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH192" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI192" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ192" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM192" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN192" t="b">
-        <v>1</v>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
@@ -34543,17 +34454,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -34587,22 +34498,39 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O193" t="n">
-        <v>4</v>
-      </c>
-      <c r="R193" t="n">
-        <v>0.07565041865887316</v>
-      </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -34610,6 +34538,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34627,7 +34613,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -34640,42 +34626,42 @@
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34702,7 +34688,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -34751,98 +34737,23 @@
       <c r="O194" t="n">
         <v>4</v>
       </c>
+      <c r="R194" t="n">
+        <v>0.07565041865887316</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U194" t="inlineStr">
         <is>
           <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
-      <c r="V194" t="inlineStr">
-        <is>
-          <t>SER_NZ_TYPHOID_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W194" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X194" t="inlineStr">
-        <is>
-          <t>Typhoid fever</t>
-        </is>
-      </c>
-      <c r="Y194" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z194" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB194" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD194" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE194" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF194" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG194" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH194" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI194" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ194" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
-        </is>
-      </c>
-      <c r="AM194" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN194" t="b">
-        <v>1</v>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
@@ -34936,17 +34847,17 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -34980,22 +34891,39 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O195" t="n">
-        <v>2</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0.01868976085656669</v>
-      </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -35003,6 +34931,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD195" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE195" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF195" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG195" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH195" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI195" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science typhoid-only monthly notifications.</t>
+        </is>
+      </c>
+      <c r="AM195" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN195" t="b">
+        <v>1</v>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -35020,7 +35006,7 @@
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+          <t>SER_NZ_TYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -35033,42 +35019,42 @@
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35095,7 +35081,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -35144,98 +35130,23 @@
       <c r="O196" t="n">
         <v>2</v>
       </c>
+      <c r="R196" t="n">
+        <v>0.01868976085656669</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U196" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TYPHOID</t>
         </is>
       </c>
-      <c r="V196" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X196" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y196" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z196" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB196" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD196" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE196" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF196" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG196" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH196" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI196" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ196" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
-        </is>
-      </c>
-      <c r="AM196" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN196" t="b">
-        <v>1</v>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
@@ -35329,17 +35240,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -35373,81 +35284,170 @@
         </is>
       </c>
       <c r="N197" t="n">
+        <v>2</v>
+      </c>
+      <c r="O197" t="n">
+        <v>2</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Typhoid-only source category.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
         <v>1</v>
       </c>
-      <c r="O197" t="n">
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT197" t="n">
         <v>1</v>
       </c>
-      <c r="R197" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP197" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS197" t="inlineStr"/>
-      <c r="AT197" t="n">
-        <v>0</v>
-      </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35479,12 +35479,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -35509,7 +35509,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -35524,7 +35524,7 @@
         <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -35557,42 +35557,42 @@
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35624,12 +35624,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -35663,13 +35663,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -35702,42 +35702,42 @@
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35769,12 +35769,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -35799,7 +35799,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -35813,9 +35813,6 @@
       <c r="O200" t="n">
         <v>0</v>
       </c>
-      <c r="P200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0</v>
       </c>
@@ -35824,77 +35821,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA200" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35921,7 +35909,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -35973,98 +35961,18 @@
       <c r="P201" t="n">
         <v>0</v>
       </c>
-      <c r="U201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R201" t="n">
+        <v>0</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
@@ -36158,17 +36066,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -36193,7 +36101,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -36202,81 +36110,173 @@
         </is>
       </c>
       <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
         <v>1</v>
       </c>
-      <c r="O202" t="n">
-        <v>1</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS202" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36308,12 +36308,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -36353,7 +36353,7 @@
         <v>1</v>
       </c>
       <c r="R203" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -36386,42 +36386,42 @@
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36453,12 +36453,12 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -36483,7 +36483,7 @@
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -36492,93 +36492,81 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O204" t="n">
-        <v>3</v>
-      </c>
-      <c r="P204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R204" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA204" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ204" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR204" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36605,7 +36593,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -36657,98 +36645,18 @@
       <c r="P205" t="n">
         <v>3</v>
       </c>
-      <c r="U205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V205" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W205" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y205" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R205" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD205" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE205" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF205" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG205" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH205" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI205" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ205" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM205" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN205" t="b">
-        <v>1</v>
       </c>
       <c r="AO205" t="inlineStr">
         <is>
@@ -36842,17 +36750,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -36877,7 +36785,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -36886,81 +36794,173 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P206" t="n">
+        <v>3</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -36992,12 +36992,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -37031,13 +37031,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -37070,42 +37070,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37137,12 +37137,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -37181,88 +37181,76 @@
       <c r="O208" t="n">
         <v>2</v>
       </c>
-      <c r="P208" t="n">
-        <v>2</v>
-      </c>
       <c r="R208" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA208" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO208" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ208" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS208" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR208" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU208" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA208" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB208" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC208" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37289,7 +37277,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -37341,98 +37329,18 @@
       <c r="P209" t="n">
         <v>2</v>
       </c>
-      <c r="U209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V209" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W209" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X209" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y209" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R209" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC209" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD209" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE209" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF209" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG209" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH209" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI209" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ209" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM209" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN209" t="b">
-        <v>1</v>
       </c>
       <c r="AO209" t="inlineStr">
         <is>
@@ -37526,17 +37434,17 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -37561,7 +37469,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -37570,81 +37478,173 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O210" t="n">
-        <v>0</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P210" t="n">
+        <v>2</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -37676,12 +37676,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -37715,13 +37715,13 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
@@ -37754,42 +37754,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37821,12 +37821,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -37851,7 +37851,7 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
@@ -37866,7 +37866,7 @@
         <v>2</v>
       </c>
       <c r="R212" t="n">
-        <v>0.001633616815131532</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -37899,42 +37899,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37966,12 +37966,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -38005,93 +38005,81 @@
         </is>
       </c>
       <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="n">
+        <v>2</v>
+      </c>
+      <c r="R213" t="n">
+        <v>0.001633616815131532</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP213" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR213" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
+      <c r="AT213" t="n">
         <v>0</v>
       </c>
-      <c r="O213" t="n">
-        <v>0</v>
-      </c>
-      <c r="P213" t="n">
-        <v>0</v>
-      </c>
-      <c r="R213" t="n">
-        <v>0</v>
-      </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA213" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP213" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
-      <c r="AT213" t="n">
-        <v>2</v>
-      </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -38118,7 +38106,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -38170,98 +38158,18 @@
       <c r="P214" t="n">
         <v>0</v>
       </c>
-      <c r="U214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V214" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W214" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X214" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y214" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z214" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R214" t="n">
+        <v>0</v>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB214" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD214" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE214" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF214" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG214" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH214" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI214" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ214" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM214" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN214" t="b">
-        <v>1</v>
       </c>
       <c r="AO214" t="inlineStr">
         <is>
@@ -38355,17 +38263,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -38390,12 +38298,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N215" t="n">
@@ -38404,76 +38312,168 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="R215" t="n">
+      <c r="P215" t="n">
         <v>0</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -38505,12 +38505,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -38544,95 +38544,81 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R216" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="AA216" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38659,7 +38645,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -38708,98 +38694,23 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
+      <c r="R217" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U217" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1180</t>
         </is>
       </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1180</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>Salmonella Typhi</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Typhi-only series.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
       </c>
       <c r="AO217" t="inlineStr">
         <is>
@@ -38893,17 +38804,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -38937,81 +38848,170 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
-      </c>
-      <c r="R218" t="n">
-        <v>0</v>
-      </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X218" t="inlineStr">
+        <is>
+          <t>Salmonella Typhi</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD218" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE218" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF218" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG218" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH218" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI218" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Typhi-only series.</t>
+        </is>
+      </c>
+      <c r="AM218" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN218" t="b">
+        <v>1</v>
       </c>
       <c r="AO218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS218" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ218" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS218" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1180</t>
+        </is>
+      </c>
       <c r="AT218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39043,12 +39043,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -39082,95 +39082,81 @@
         </is>
       </c>
       <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>1</v>
+      </c>
+      <c r="R219" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP219" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR219" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
+      <c r="AT219" t="n">
         <v>0</v>
       </c>
-      <c r="O219" t="n">
-        <v>0</v>
-      </c>
-      <c r="R219" t="n">
-        <v>0</v>
-      </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA219" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP219" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT219" t="n">
-        <v>1</v>
-      </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39197,7 +39183,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -39246,98 +39232,23 @@
       <c r="O220" t="n">
         <v>0</v>
       </c>
+      <c r="R220" t="n">
+        <v>0</v>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U220" t="inlineStr">
         <is>
           <t>SER_NO_FHI_711_MONTHLY</t>
         </is>
       </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_711_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Tyfoidfeber</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
       </c>
       <c r="AO220" t="inlineStr">
         <is>
@@ -39431,17 +39342,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -39475,81 +39386,170 @@
         </is>
       </c>
       <c r="N221" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Tyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS typhoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
         <v>1</v>
       </c>
-      <c r="O221" t="n">
+      <c r="AO221" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP221" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_711_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT221" t="n">
         <v>1</v>
       </c>
-      <c r="R221" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP221" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
-      <c r="AT221" t="n">
-        <v>0</v>
-      </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -39581,12 +39581,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -39611,7 +39611,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -39620,13 +39620,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R222" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -39659,42 +39659,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39726,12 +39726,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -39770,9 +39770,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="P223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -39781,77 +39778,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA223" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ223" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39878,7 +39866,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -39930,98 +39918,18 @@
       <c r="P224" t="n">
         <v>0</v>
       </c>
-      <c r="U224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V224" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X224" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y224" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z224" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R224" t="n">
+        <v>0</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB224" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC224" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD224" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE224" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF224" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG224" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH224" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI224" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ224" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK224" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM224" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN224" t="b">
-        <v>1</v>
       </c>
       <c r="AO224" t="inlineStr">
         <is>
@@ -40115,17 +40023,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40150,7 +40058,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -40159,81 +40067,173 @@
         </is>
       </c>
       <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT225" t="n">
         <v>2</v>
       </c>
-      <c r="O225" t="n">
-        <v>2</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.001633616815131532</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP225" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
-      <c r="AT225" t="n">
-        <v>0</v>
-      </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40265,12 +40265,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40304,93 +40304,81 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O226" t="n">
-        <v>1</v>
-      </c>
-      <c r="P226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R226" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.001633616815131532</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA226" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ226" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40417,7 +40405,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -40469,98 +40457,18 @@
       <c r="P227" t="n">
         <v>1</v>
       </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R227" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
@@ -40654,17 +40562,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40689,7 +40597,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -40698,81 +40606,173 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
-      </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P228" t="n">
+        <v>1</v>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W228" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X228" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y228" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC228" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD228" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE228" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF228" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG228" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH228" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI228" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ228" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM228" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN228" t="b">
+        <v>1</v>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS228" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ228" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
       <c r="AT228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -40804,12 +40804,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40848,9 +40848,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="P229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -40859,77 +40856,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA229" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ229" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS229" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40956,7 +40944,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -41008,98 +40996,18 @@
       <c r="P230" t="n">
         <v>0</v>
       </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="V230" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_TYPHOID</t>
-        </is>
-      </c>
-      <c r="W230" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X230" t="inlineStr">
-        <is>
-          <t>Typhoid</t>
-        </is>
-      </c>
-      <c r="Y230" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z230" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R230" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB230" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC230" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD230" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE230" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF230" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG230" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH230" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI230" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ230" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK230" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM230" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN230" t="b">
-        <v>1</v>
       </c>
       <c r="AO230" t="inlineStr">
         <is>
@@ -41193,123 +41101,360 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>伤寒</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>0</v>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID</t>
+        </is>
+      </c>
+      <c r="W231" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X231" t="inlineStr">
+        <is>
+          <t>Typhoid</t>
+        </is>
+      </c>
+      <c r="Y231" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC231" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD231" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE231" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF231" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG231" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH231" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI231" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ231" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM231" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN231" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ231" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_TYPHOID; SER_SG_HIST_TYPHOID</t>
+        </is>
+      </c>
+      <c r="AT231" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>typhoid-fever</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F232" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G232" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>D124</t>
-        </is>
-      </c>
-      <c r="I231" t="inlineStr">
-        <is>
-          <t>Typhoid fever</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Typhoid fever</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
         <is>
           <t>伤寒</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="K232" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="M231" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N231" t="n">
+      <c r="N232" t="n">
         <v>2</v>
       </c>
-      <c r="O231" t="n">
+      <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="R231" t="n">
+      <c r="R232" t="n">
         <v>0.0005730076265538771</v>
       </c>
-      <c r="S231" t="inlineStr">
+      <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO231" t="inlineStr">
+      <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP231" t="inlineStr">
+      <c r="AP232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR231" t="inlineStr">
+      <c r="AR232" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS231" t="inlineStr"/>
-      <c r="AT231" t="n">
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="n">
         <v>0</v>
       </c>
-      <c r="AU231" t="inlineStr">
+      <c r="AU232" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV231" t="inlineStr">
+      <c r="AV232" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW231" t="inlineStr">
+      <c r="AW232" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX231" t="inlineStr">
+      <c r="AX232" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY231" t="inlineStr">
+      <c r="AY232" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ231" t="inlineStr">
+      <c r="AZ232" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA231" t="inlineStr">
+      <c r="BA232" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB231" t="inlineStr">
+      <c r="BB232" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC231" t="inlineStr">
+      <c r="BC232" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -41431,7 +41576,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -41441,7 +41586,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -41493,7 +41638,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d124/2026-2029.xlsx
+++ b/diseases/d124/2026-2029.xlsx
@@ -44483,13 +44483,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R253" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -45670,7 +45670,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16">
